--- a/backtest_runs/20260410_193731/by_symbol/LPGL/LPGL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/LPGL/LPGL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>100000</v>
@@ -679,7 +679,7 @@
         <v>-5366.549999999993</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>94633.45000000001</v>
@@ -817,7 +817,7 @@
         <v>-9361.199999999992</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>91593.75</v>
@@ -955,7 +955,7 @@
         <v>-6334.949999999992</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>85258.8</v>
@@ -1185,7 +1185,7 @@
         <v>-1318.099999999986</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>90679.15000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-9415</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>83106.79999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-1385.350000000002</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>86159.95000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-4451.950000000003</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>95265.60000000001</v>
